--- a/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 18,67</t>
+          <t>1,75; 21,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 22,21</t>
+          <t>2,22; 22,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,47; -11,18</t>
+          <t>-23,65; -10,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,45; 30,04</t>
+          <t>12,7; 30,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,03; 34,18</t>
+          <t>14,48; 34,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,83; -18,5</t>
+          <t>-34,31; -19,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 24,37</t>
+          <t>10,11; 23,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,81; 26,39</t>
+          <t>12,23; 26,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,97; -17,42</t>
+          <t>-27,32; -17,32</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 118,62</t>
+          <t>4,43; 128,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,9; 135,9</t>
+          <t>8,65; 139,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-94,87; -68,58</t>
+          <t>-95,21; -65,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,88; 102,63</t>
+          <t>32,06; 109,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,32; 123,17</t>
+          <t>37,06; 122,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,0; -64,49</t>
+          <t>-89,86; -66,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,37; 101,85</t>
+          <t>34,21; 99,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,03; 115,51</t>
+          <t>40,6; 112,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,58; -74,17</t>
+          <t>-89,78; -73,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 17,75</t>
+          <t>1,53; 17,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,38; 24,24</t>
+          <t>8,16; 23,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-56,56; -43,25</t>
+          <t>-57,17; -43,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,79; 20,96</t>
+          <t>10,22; 20,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 16,09</t>
+          <t>5,06; 15,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-67,48; -54,28</t>
+          <t>-68,13; -54,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 17,72</t>
+          <t>8,47; 17,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 18,02</t>
+          <t>8,46; 17,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-60,83; -51,49</t>
+          <t>-60,67; -51,71</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 33,03</t>
+          <t>2,67; 31,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 45,33</t>
+          <t>13,12; 43,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-90,96; -79,32</t>
+          <t>-91,17; -78,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,32; 28,89</t>
+          <t>12,78; 29,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 21,99</t>
+          <t>6,31; 21,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,73; -72,83</t>
+          <t>-86,58; -72,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,88; 26,94</t>
+          <t>11,76; 27,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 27,49</t>
+          <t>11,84; 27,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-86,42; -77,24</t>
+          <t>-85,88; -77,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 19,79</t>
+          <t>8,72; 20,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 17,44</t>
+          <t>5,2; 18,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-48,71; -37,69</t>
+          <t>-48,95; -37,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,26; 30,07</t>
+          <t>21,42; 29,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,33; 15,5</t>
+          <t>5,41; 15,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,35; -44,61</t>
+          <t>-55,79; -44,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,24; 23,43</t>
+          <t>16,34; 23,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 14,76</t>
+          <t>7,23; 15,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-50,58; -42,76</t>
+          <t>-50,39; -42,67</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,99; 34,92</t>
+          <t>13,86; 36,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 30,66</t>
+          <t>8,23; 32,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,19; -65,63</t>
+          <t>-77,57; -65,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,24; 46,11</t>
+          <t>29,67; 45,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 23,69</t>
+          <t>7,44; 22,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,78; -66,59</t>
+          <t>-78,9; -66,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,02; 37,31</t>
+          <t>23,66; 36,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,2; 23,48</t>
+          <t>10,72; 23,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,21; -67,75</t>
+          <t>-75,82; -67,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,21; 30,54</t>
+          <t>15,21; 31,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 18,42</t>
+          <t>1,82; 18,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-42,68; -27,84</t>
+          <t>-41,51; -26,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,29; 39,96</t>
+          <t>24,59; 40,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 16,14</t>
+          <t>-1,07; 16,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -34,41</t>
+          <t>-48,01; -34,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,76; 33,44</t>
+          <t>21,72; 33,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 15,25</t>
+          <t>2,75; 15,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-43,18; -32,76</t>
+          <t>-43,65; -31,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,77; 84,58</t>
+          <t>33,23; 84,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,99; 50,78</t>
+          <t>4,07; 52,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,78; -72,25</t>
+          <t>-91,67; -71,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42,11; 82,77</t>
+          <t>41,28; 85,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 32,7</t>
+          <t>-1,76; 33,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,11; -71,64</t>
+          <t>-81,59; -71,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,03; 78,76</t>
+          <t>42,88; 78,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,85; 35,51</t>
+          <t>5,76; 35,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-88,04; -73,88</t>
+          <t>-87,18; -73,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,9; 37,04</t>
+          <t>12,67; 36,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 24,05</t>
+          <t>1,22; 23,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,59; -7,34</t>
+          <t>-23,83; -6,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 19,96</t>
+          <t>0,48; 19,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 5,55</t>
+          <t>-15,44; 4,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-34,02; -20,68</t>
+          <t>-33,96; -20,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,21; 23,35</t>
+          <t>7,97; 22,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 8,45</t>
+          <t>-6,15; 8,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-28,78; -17,91</t>
+          <t>-29,22; -18,14</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>45,1; 264,18</t>
+          <t>47,71; 279,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,68; 162,52</t>
+          <t>0,65; 163,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,02; -52,27</t>
+          <t>-84,15; -49,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 66,05</t>
+          <t>0,82; 65,18</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 18,71</t>
+          <t>-39,23; 16,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-83,18; -69,53</t>
+          <t>-83,25; -69,85</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,04; 89,15</t>
+          <t>24,7; 90,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 32,68</t>
+          <t>-18,47; 32,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,22; -70,36</t>
+          <t>-82,69; -70,78</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,01; 9,05</t>
+          <t>0,09; 9,21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 6,0</t>
+          <t>-2,07; 6,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 0,4</t>
+          <t>-5,51; 0,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 5,17</t>
+          <t>-5,38; 5,19</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 4,02</t>
+          <t>-5,88; 4,27</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 61,95</t>
+          <t>-8,64; 59,08</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 5,25</t>
+          <t>-1,4; 5,66</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,04</t>
+          <t>-2,77; 4,05</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 47,73</t>
+          <t>-5,78; 50,09</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 209,37</t>
+          <t>-3,68; 207,14</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 141,1</t>
+          <t>-29,22; 146,58</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-68,52; 9,77</t>
+          <t>-67,86; 13,9</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 44,79</t>
+          <t>-32,12; 46,86</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-37,28; 34,52</t>
+          <t>-35,95; 38,53</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,83; 557,35</t>
+          <t>-58,6; 538,77</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 61,34</t>
+          <t>-11,7; 65,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 46,95</t>
+          <t>-23,58; 46,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-53,12; 512,27</t>
+          <t>-53,01; 539,84</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 3,55</t>
+          <t>-7,59; 3,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 1,99</t>
+          <t>-8,05; 1,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 1,26</t>
+          <t>-8,45; 0,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 7,77</t>
+          <t>-1,43; 8,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 9,58</t>
+          <t>-0,3; 9,62</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 2,31</t>
+          <t>-5,14; 2,0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 4,76</t>
+          <t>-2,1; 4,89</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,35</t>
+          <t>-1,98; 5,53</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 0,63</t>
+          <t>-5,67; 0,3</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-58,89; 46,69</t>
+          <t>-60,13; 47,79</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-61,14; 29,67</t>
+          <t>-60,08; 24,24</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-60,69; 23,22</t>
+          <t>-60,01; 12,13</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 127,23</t>
+          <t>-14,0; 136,62</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 152,14</t>
+          <t>-5,3; 155,04</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 39,8</t>
+          <t>-45,03; 35,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 60,78</t>
+          <t>-19,46; 66,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 69,93</t>
+          <t>-21,29; 71,5</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-44,61; 9,18</t>
+          <t>-47,99; 4,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>9,57; 15,35</t>
+          <t>9,39; 15,38</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,02; 10,25</t>
+          <t>4,17; 10,35</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-32,18; -26,61</t>
+          <t>-31,87; -26,56</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12,93; 18,71</t>
+          <t>12,66; 18,2</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,14; 8,1</t>
+          <t>1,98; 8,07</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-35,15; -13,5</t>
+          <t>-34,97; -13,19</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,69; 16,22</t>
+          <t>12,01; 16,18</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>4,21; 8,7</t>
+          <t>3,73; 8,18</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-32,69; -19,94</t>
+          <t>-32,76; -21,31</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>24,91; 43,07</t>
+          <t>24,23; 43,04</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10,66; 29,1</t>
+          <t>10,93; 28,89</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-83,52; -75,76</t>
+          <t>-83,61; -75,7</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>27,3; 42,07</t>
+          <t>26,64; 41,24</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,33; 17,99</t>
+          <t>4,12; 18,1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-75,41; -29,28</t>
+          <t>-75,25; -29,03</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,07; 40,0</t>
+          <t>28,2; 40,1</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>9,75; 21,24</t>
+          <t>8,52; 20,02</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-77,62; -48,08</t>
+          <t>-77,41; -50,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-17,11</t>
+          <t>-16,66</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-26,8</t>
+          <t>-25,88</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-22,15</t>
+          <t>-21,36</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 21,66</t>
+          <t>1,53; 19,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 22,44</t>
+          <t>2,05; 21,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,65; -10,58</t>
+          <t>-23,5; -11,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,7; 30,03</t>
+          <t>11,27; 31,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,48; 34,23</t>
+          <t>14,31; 34,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,31; -19,11</t>
+          <t>-33,46; -18,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,11; 23,19</t>
+          <t>11,01; 24,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 26,4</t>
+          <t>12,4; 26,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-27,32; -17,32</t>
+          <t>-26,41; -16,09</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-85,51%</t>
+          <t>-83,27%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-80,19%</t>
+          <t>-77,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-83,01%</t>
+          <t>-80,06%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 128,4</t>
+          <t>6,21; 121,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,65; 139,86</t>
+          <t>7,57; 134,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-95,21; -65,91</t>
+          <t>-92,48; -63,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,06; 109,62</t>
+          <t>29,18; 109,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,06; 122,37</t>
+          <t>37,85; 120,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,86; -66,64</t>
+          <t>-87,44; -61,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,21; 99,46</t>
+          <t>36,3; 103,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,6; 112,86</t>
+          <t>42,2; 115,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,78; -73,2</t>
+          <t>-87,03; -69,06</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-50,43</t>
+          <t>-48,8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-60,01</t>
+          <t>-56,67</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-56,09</t>
+          <t>-53,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 17,13</t>
+          <t>2,29; 17,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,16; 23,76</t>
+          <t>7,79; 23,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-57,17; -43,62</t>
+          <t>-55,63; -42,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 20,97</t>
+          <t>10,58; 21,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 15,57</t>
+          <t>5,12; 15,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,13; -54,11</t>
+          <t>-61,77; -50,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 17,74</t>
+          <t>8,56; 17,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 17,77</t>
+          <t>8,11; 17,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -51,71</t>
+          <t>-58,49; -49,49</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-86,38%</t>
+          <t>-83,6%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-78,41%</t>
+          <t>-74,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-81,6%</t>
+          <t>-78,39%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 31,82</t>
+          <t>3,7; 33,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,12; 43,97</t>
+          <t>12,68; 44,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-91,17; -78,34</t>
+          <t>-88,9; -76,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,78; 29,0</t>
+          <t>13,16; 28,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 21,42</t>
+          <t>6,38; 21,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,58; -72,87</t>
+          <t>-78,53; -68,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,76; 27,01</t>
+          <t>11,75; 26,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,84; 27,32</t>
+          <t>11,55; 26,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-85,88; -77,26</t>
+          <t>-82,1; -74,15</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-43,33</t>
+          <t>-43,14</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-49,45</t>
+          <t>-47,18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-46,64</t>
+          <t>-45,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 20,34</t>
+          <t>8,56; 20,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 18,05</t>
+          <t>5,48; 17,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-48,95; -37,22</t>
+          <t>-48,55; -38,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,42; 29,89</t>
+          <t>21,45; 29,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,41; 15,02</t>
+          <t>5,44; 15,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,79; -44,4</t>
+          <t>-52,14; -42,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,34; 23,14</t>
+          <t>16,07; 23,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 15,03</t>
+          <t>6,75; 14,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-50,39; -42,67</t>
+          <t>-49,19; -41,46</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-71,89%</t>
+          <t>-71,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-71,35%</t>
+          <t>-68,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-71,63%</t>
+          <t>-69,85%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,86; 36,33</t>
+          <t>13,4; 36,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,23; 32,27</t>
+          <t>8,57; 30,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,57; -65,05</t>
+          <t>-77,2; -65,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,67; 45,4</t>
+          <t>29,54; 44,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,44; 22,6</t>
+          <t>7,6; 23,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,9; -66,34</t>
+          <t>-72,5; -63,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,66; 36,68</t>
+          <t>23,73; 37,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,72; 23,86</t>
+          <t>10,06; 23,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,82; -67,63</t>
+          <t>-73,22; -65,9</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-33,69</t>
+          <t>-30,37</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-41,38</t>
+          <t>-40,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-37,18</t>
+          <t>-34,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,21; 31,38</t>
+          <t>15,65; 31,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 18,78</t>
+          <t>1,76; 17,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-41,51; -26,85</t>
+          <t>-37,25; -24,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,59; 40,72</t>
+          <t>25,14; 40,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 16,42</t>
+          <t>-0,88; 16,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -34,97</t>
+          <t>-47,32; -33,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,72; 33,51</t>
+          <t>22,42; 33,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 15,51</t>
+          <t>3,65; 15,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-43,65; -31,99</t>
+          <t>-39,28; -29,76</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-81,78%</t>
+          <t>-73,73%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-76,93%</t>
+          <t>-74,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-79,33%</t>
+          <t>-73,68%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>33,23; 84,82</t>
+          <t>34,52; 90,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,07; 52,64</t>
+          <t>3,83; 48,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,67; -71,73</t>
+          <t>-80,19; -66,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41,28; 85,09</t>
+          <t>41,96; 84,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 33,59</t>
+          <t>-1,42; 34,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,59; -71,81</t>
+          <t>-79,23; -69,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,88; 78,38</t>
+          <t>44,61; 77,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,76; 35,55</t>
+          <t>7,19; 35,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-87,18; -73,54</t>
+          <t>-77,56; -69,27</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-14,48</t>
+          <t>-14,36</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-27,19</t>
+          <t>-26,8</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-23,09</t>
+          <t>-22,82</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,67; 36,69</t>
+          <t>14,18; 36,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 23,76</t>
+          <t>0,58; 23,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-23,83; -6,9</t>
+          <t>-23,56; -7,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 19,76</t>
+          <t>0,23; 20,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 4,73</t>
+          <t>-14,98; 4,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-33,96; -20,12</t>
+          <t>-33,97; -19,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,97; 22,97</t>
+          <t>7,45; 22,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 8,54</t>
+          <t>-7,16; 7,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-29,22; -18,14</t>
+          <t>-28,37; -17,75</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-72,14%</t>
+          <t>-71,56%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-77,61%</t>
+          <t>-76,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-77,49%</t>
+          <t>-76,61%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>47,71; 279,09</t>
+          <t>53,64; 255,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,65; 163,82</t>
+          <t>1,57; 161,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,15; -49,9</t>
+          <t>-83,72; -51,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,82; 65,18</t>
+          <t>0,31; 66,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 16,1</t>
+          <t>-36,47; 15,7</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-83,25; -69,85</t>
+          <t>-82,05; -67,76</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,7; 90,17</t>
+          <t>22,78; 89,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 32,78</t>
+          <t>-20,97; 29,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,69; -70,78</t>
+          <t>-81,75; -69,62</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,22</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,14</t>
+          <t>-6,93</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14,87</t>
+          <t>-4,77</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,09; 9,21</t>
+          <t>0,58; 9,72</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 6,14</t>
+          <t>-2,19; 6,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,49</t>
+          <t>-5,58; 0,7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 5,19</t>
+          <t>-5,16; 5,12</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 4,27</t>
+          <t>-6,13; 4,71</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 59,08</t>
+          <t>-10,98; -2,96</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 5,66</t>
+          <t>-1,41; 5,1</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 4,05</t>
+          <t>-2,68; 3,73</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 50,09</t>
+          <t>-7,28; -2,31</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-36,79%</t>
+          <t>-35,03%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>172,33%</t>
+          <t>-49,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>143,9%</t>
+          <t>-46,18%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 207,14</t>
+          <t>2,9; 219,91</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 146,58</t>
+          <t>-27,62; 143,25</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,86; 13,9</t>
+          <t>-64,05; 22,94</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 46,86</t>
+          <t>-31,69; 44,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 38,53</t>
+          <t>-38,07; 39,66</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-58,6; 538,77</t>
+          <t>-64,6; -24,2</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 65,76</t>
+          <t>-11,48; 58,34</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 46,17</t>
+          <t>-23,1; 40,16</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-53,01; 539,84</t>
+          <t>-61,09; -27,59</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-3,51</t>
+          <t>-3,57</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,31</t>
+          <t>-1,42</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,17</t>
+          <t>-2,25</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 3,84</t>
+          <t>-7,69; 4,05</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 1,79</t>
+          <t>-8,34; 1,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 0,79</t>
+          <t>-8,17; 0,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 8,54</t>
+          <t>-1,69; 7,62</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 9,62</t>
+          <t>-0,6; 9,55</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 2,0</t>
+          <t>-5,55; 1,81</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,89</t>
+          <t>-2,65; 4,98</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 5,53</t>
+          <t>-1,83; 5,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 0,3</t>
+          <t>-5,24; 0,38</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-33,93%</t>
+          <t>-34,5%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-15,4%</t>
+          <t>-16,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-23,47%</t>
+          <t>-24,41%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-60,13; 47,79</t>
+          <t>-59,19; 56,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-60,08; 24,24</t>
+          <t>-62,21; 26,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-60,01; 12,13</t>
+          <t>-61,64; 8,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 136,62</t>
+          <t>-15,06; 123,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 155,04</t>
+          <t>-8,42; 150,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-45,03; 35,98</t>
+          <t>-47,65; 30,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,46; 66,13</t>
+          <t>-23,64; 65,62</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 71,5</t>
+          <t>-17,22; 75,71</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-47,99; 4,11</t>
+          <t>-46,43; 5,94</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-29,23</t>
+          <t>-28,09</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-29,38</t>
+          <t>-33,14</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-29,57</t>
+          <t>-30,98</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>9,39; 15,38</t>
+          <t>9,5; 15,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,17; 10,35</t>
+          <t>4,16; 10,17</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-31,87; -26,56</t>
+          <t>-30,72; -25,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12,66; 18,2</t>
+          <t>12,7; 18,32</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,07</t>
+          <t>2,49; 8,27</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -13,19</t>
+          <t>-35,41; -30,83</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,01; 16,18</t>
+          <t>11,99; 16,21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,18</t>
+          <t>4,15; 8,5</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-32,76; -21,31</t>
+          <t>-32,67; -29,27</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-79,08%</t>
+          <t>-76,01%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-63,86%</t>
+          <t>-72,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-70,56%</t>
+          <t>-73,94%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>24,23; 43,04</t>
+          <t>25,1; 44,59</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10,93; 28,89</t>
+          <t>10,56; 28,91</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-83,61; -75,7</t>
+          <t>-79,08; -73,04</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26,64; 41,24</t>
+          <t>26,82; 41,64</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,12; 18,1</t>
+          <t>5,18; 18,58</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-75,25; -29,03</t>
+          <t>-74,48; -69,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,2; 40,1</t>
+          <t>27,87; 39,88</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>8,52; 20,02</t>
+          <t>9,74; 20,92</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-77,41; -50,83</t>
+          <t>-75,69; -71,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
